--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="23"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -15,25 +15,29 @@
     <sheet name="TGZ-S-48-100_250RI" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="TGZ-S-48-100_300RI" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="TGZ-S-48-100_250" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="TGZ-S-48-100_300" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="TGZ-S-48-100_425" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="TGZ-S-230-5_15" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="TGZ-D-320-5_10" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="TGZ-D-320-5_15" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="TGZ-S-400-3_9" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="TGZ-S-400-7_15" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="TGZ-S-400-10_20" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="TGZ-S-400-14_30" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="TGS-320-10_15" sheetId="18" state="visible" r:id="rId20"/>
-    <sheet name="TGS-560-25_50" sheetId="19" state="visible" r:id="rId21"/>
-    <sheet name="TGS-560-50_100" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TGMmini" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="TGMcontroller" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="TGZpMotion" sheetId="23" state="visible" r:id="rId25"/>
-    <sheet name="commonHW_DI" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="commonHW_DO" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="commonHW_AI" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="TGZ-S-48-100_250-O" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="TGZ-S-48-100_300" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="TGZ-S-48-100_300-O" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="TGZ-S-48-100_425" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="TGZ-S-48-100_425-O" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="TGZ-S-230-5_15" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="TGZ-D-320-5_10" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="TGZ-D-320-5_15" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="TGZ-S-400-3_9" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="TGZ-S-400-7_15" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="TGZ-S-400-10_20" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="TGZ-S-400-14_30" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="TGZ-D-560-3_9" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGS-320-10_15" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="TGS-560-25_50" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="TGS-560-50_100" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="TGMmini" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="TGMcontroller" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="TGZpMotion" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="commonHW_DI" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="commonHW_DO" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="commonHW_AI" sheetId="30" state="visible" r:id="rId32"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -45,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="291">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -362,6 +366,21 @@
     <t xml:space="preserve">1 x 12pin WEIDMÜLLER  B2CF 3.50/12/180</t>
   </si>
   <si>
+    <t xml:space="preserve">2x svorka DIN Molex 201606-0610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x svorka DIN WEIDMÜLLER WDU 1.5/R3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x svorka DIN Molex 201606-6163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x svorka DIN WEIDMÜLLER WDU 1.5/R3.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STO A, B</t>
+  </si>
+  <si>
     <t xml:space="preserve">425 A</t>
   </si>
   <si>
@@ -497,34 +516,37 @@
     <t xml:space="preserve">24-560 VDC</t>
   </si>
   <si>
+    <t xml:space="preserve">10kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSTUPY/VÝSTUPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">šroubovací svorky M8x12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 4pin  WEIDMÜLLER LSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 8pin WEIDMÜLLER B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER B2CF 3.50/12/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560</t>
+  </si>
+  <si>
     <t xml:space="preserve">33 kW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">900 W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VSTUPY/VÝSTUPY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">šroubovací svorky M8x12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 4pin  WEIDMÜLLER LSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 x 8pin WEIDMÜLLER B2CF 3.50/08/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 12pin WEIDMÜLLER B2CF 3.50/12/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560</t>
   </si>
   <si>
     <t xml:space="preserve">Vstupní napětí (VAC - 50/60 Hz) </t>
@@ -1388,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1396,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1404,7 +1426,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,7 +1434,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1420,7 +1442,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1428,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1484,7 +1506,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1508,7 +1530,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1524,7 +1546,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1532,44 +1554,55 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>113</v>
+      <c r="B25" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>115</v>
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1588,10 +1621,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1608,7 +1641,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,7 +1649,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1624,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1632,143 +1665,143 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1776,7 +1809,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1784,7 +1817,15 @@
         <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>104</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1803,10 +1844,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
@@ -1823,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1831,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1839,7 +1880,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1847,143 +1888,143 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2000,6 +2041,22 @@
       </c>
       <c r="B28" s="1" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2018,237 +2075,208 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>126</v>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>127</v>
+      <c r="B4" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>128</v>
+      <c r="B5" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>129</v>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>57</v>
+      <c r="B7" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1</v>
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1</v>
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
+      <c r="B23" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>112</v>
+      <c r="A25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>133</v>
+      <c r="A26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="1" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>134</v>
+      <c r="A30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2267,75 +2295,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>135</v>
+      <c r="B3" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>136</v>
+      <c r="B4" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>137</v>
+      <c r="B5" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>131</v>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2346,158 +2374,124 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
+      <c r="B24" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>112</v>
+      <c r="B25" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>133</v>
+      <c r="B26" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>114</v>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2516,75 +2510,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
+      <c r="B2" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>138</v>
+      <c r="B3" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>139</v>
+      <c r="B4" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
+      <c r="B5" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>131</v>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2595,158 +2589,124 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>132</v>
+      <c r="B24" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>112</v>
+      <c r="B25" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>133</v>
+      <c r="B26" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>114</v>
+      <c r="B27" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2793,7 +2753,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2801,7 +2761,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2809,7 +2769,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2817,7 +2777,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,15 +2785,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>146</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2945,7 +2905,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2953,7 +2913,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2961,7 +2921,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2969,7 +2929,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2986,16 +2946,16 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3014,75 +2974,75 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>148</v>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>149</v>
+      <c r="B3" s="3" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>150</v>
+      <c r="B4" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>145</v>
+      <c r="B5" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>151</v>
+      <c r="A6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>152</v>
+      <c r="A8" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,145 +3053,158 @@
         <v>17</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+    </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+    </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="A21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>154</v>
+      <c r="B24" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>155</v>
+      <c r="B25" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>51</v>
+      <c r="B26" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>156</v>
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>157</v>
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>159</v>
+      <c r="A31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3250,191 +3223,237 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>83</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>143</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>145</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>146</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>136</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>182</v>
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>123</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>190</v>
+      <c r="A23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3453,199 +3472,237 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>174</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>182</v>
-      </c>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>182</v>
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>190</v>
+      <c r="B25" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3887,12 +3944,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3908,130 +3964,111 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>160</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>162</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>155</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>164</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>166</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>168</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>170</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>172</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>176</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>178</v>
+      <c r="A12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>182</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>182</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,66 +4081,87 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>155</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>202</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>189</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>190</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>203</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>205</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4122,12 +4180,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4140,148 +4197,207 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>206</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>153</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>165</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="3"/>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>211</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>213</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>217</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>224</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>225</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>226</v>
+        <v>29</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>227</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4300,7 +4416,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4317,151 +4433,174 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>207</v>
+      <c r="A2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>209</v>
+      <c r="A3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>207</v>
+      <c r="A4" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
+      <c r="A6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
+      <c r="A7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
+      <c r="A8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
+      <c r="A9" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>218</v>
+      <c r="A10" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>188</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>104</v>
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4480,7 +4619,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4497,65 +4636,71 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>206</v>
+      <c r="A2" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>208</v>
+      <c r="A3" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>210</v>
+      <c r="A4" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+      <c r="A8" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -4563,61 +4708,110 @@
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>217</v>
+      <c r="A10" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
+      <c r="A14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3"/>
+        <v>188</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4632,6 +4826,755 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4652,107 +5595,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,16 +5703,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -4795,16 +5738,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -4830,16 +5773,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -4865,16 +5808,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -4900,16 +5843,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -4935,16 +5878,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -4970,16 +5913,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -5005,16 +5948,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -5046,12 +5989,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
@@ -5066,117 +6009,117 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>264</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>266</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="G1" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>270</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>243</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>271</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>272</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>274</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>275</v>
-      </c>
-      <c r="H2" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I2" s="0" t="s">
-        <v>276</v>
+      <c r="C2" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>253</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>254</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>256</v>
-      </c>
-      <c r="I3" s="0" t="s">
         <v>257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="F4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0" t="n">
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5184,28 +6127,28 @@
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="F5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="I5" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5213,28 +6156,28 @@
       <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="F6" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="0" t="n">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5242,28 +6185,28 @@
       <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="F7" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="0" t="n">
+      <c r="I7" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5271,28 +6214,28 @@
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="F8" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="0" t="n">
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5300,157 +6243,29 @@
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>277</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="F9" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="0" t="n">
+      <c r="I9" s="1" t="n">
         <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0"/>
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-      <c r="I10" s="0"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0"/>
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
-      <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -5679,6 +6494,101 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -6643,7 +7553,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.16"/>
@@ -6695,7 +7605,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6759,7 +7669,7 @@
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6783,7 +7693,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6799,7 +7709,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6807,7 +7717,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6815,7 +7725,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6823,7 +7733,7 @@
         <v>52</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6831,7 +7741,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6839,7 +7749,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>43</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6847,7 +7757,15 @@
         <v>93</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -6918,7 +7836,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="19"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,16 +28,18 @@
     <sheet name="TGZ-S-400-10_20" sheetId="18" state="visible" r:id="rId20"/>
     <sheet name="TGZ-S-400-14_30" sheetId="19" state="visible" r:id="rId21"/>
     <sheet name="TGZ-D-560-3_9" sheetId="20" state="visible" r:id="rId22"/>
-    <sheet name="TGZ-D-560-30_50" sheetId="21" state="visible" r:id="rId23"/>
-    <sheet name="TGS-320-10_15" sheetId="22" state="visible" r:id="rId24"/>
-    <sheet name="TGS-560-25_50" sheetId="23" state="visible" r:id="rId25"/>
-    <sheet name="TGS-560-50_100" sheetId="24" state="visible" r:id="rId26"/>
-    <sheet name="TGMmini" sheetId="25" state="visible" r:id="rId27"/>
-    <sheet name="TGMcontroller" sheetId="26" state="visible" r:id="rId28"/>
-    <sheet name="TGZpMotion" sheetId="27" state="visible" r:id="rId29"/>
-    <sheet name="commonHW_DI" sheetId="28" state="visible" r:id="rId30"/>
-    <sheet name="commonHW_DO" sheetId="29" state="visible" r:id="rId31"/>
-    <sheet name="commonHW_AI" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="TGZ-D-560-7_15" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="TGZ-D-560-10_20" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="TGZ-D-560-30_50" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="TGS-320-10_15" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="TGS-560-25_50" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="TGS-560-50_100" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="TGMmini" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="TGMcontroller" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="TGZpMotion" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="commonHW_DI" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="commonHW_DO" sheetId="31" state="visible" r:id="rId33"/>
+    <sheet name="commonHW_AI" sheetId="32" state="visible" r:id="rId34"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="291">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -4216,7 +4218,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4416,12 +4418,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4433,174 +4434,208 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C2" s="3"/>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="3"/>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="3"/>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="3"/>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="3"/>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C11" s="3"/>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>193</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>194</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>196</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4619,12 +4654,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4636,163 +4670,144 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>166</v>
+      <c r="A2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>153</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>168</v>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>170</v>
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="3"/>
+        <v>165</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>172</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5" s="3"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>174</v>
+      <c r="A6" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="3"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>176</v>
+      <c r="A7" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="3"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>178</v>
+      <c r="A8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="3"/>
+        <v>157</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>180</v>
+      <c r="A9" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C10" s="3"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>184</v>
+      <c r="A11" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>204</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>192</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -4800,18 +4815,63 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>196</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4830,7 +4890,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -4847,206 +4907,174 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="A2" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>168</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>170</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>174</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>176</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>201</v>
+        <v>180</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>181</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>182</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>206</v>
+        <v>184</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>185</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>184</v>
+      <c r="A12" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3"/>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>188</v>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="1" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="1" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -5065,7 +5093,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5082,65 +5110,71 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>212</v>
+      <c r="A2" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>214</v>
+      <c r="A3" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>216</v>
+      <c r="A4" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>217</v>
+      <c r="A7" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>219</v>
+      <c r="A8" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -5148,83 +5182,110 @@
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>221</v>
+      <c r="A10" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>223</v>
+      <c r="A11" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>226</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>229</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>230</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>233</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -5243,7 +5304,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5261,150 +5322,205 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="3"/>
+        <v>153</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>214</v>
+      <c r="A3" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>216</v>
+      <c r="A4" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>198</v>
+      </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+      <c r="A6" s="3" t="s">
+        <v>172</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>21</v>
+      <c r="A7" s="3" t="s">
+        <v>174</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
+      <c r="A8" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
+      <c r="A9" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>223</v>
+      <c r="A10" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>224</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
+      <c r="A12" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>207</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>229</v>
+        <v>187</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>99</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>103</v>
+      <c r="A19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>104</v>
+      <c r="A20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -5423,7 +5539,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5480,19 +5596,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>219</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5507,60 +5623,82 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>228</v>
       </c>
       <c r="C15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>231</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>99</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -5579,403 +5717,168 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>245</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>256</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>263</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
+      <c r="A4" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D4" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>50</v>
-      </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>6</v>
+      <c r="A9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>7</v>
+      <c r="A10" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>50</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>50</v>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5994,278 +5897,144 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>263</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="n">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>300</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>10</v>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -6499,6 +6268,711 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>8.2</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="26.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="301">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -515,10 +515,64 @@
     <t xml:space="preserve">24 VDC ± 10 %, 2 A*</t>
   </si>
   <si>
+    <t xml:space="preserve">140-600 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 9 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VSTUPY/VÝSTUPY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin WEIDMÜLLER BLZ 7.62HP/03/180LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 6pin WEIDMÜLLER  BLZ 7.62HP/06/180LR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 8pin WEIDMÜLLER B2CF 3.50/08/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 12pin WEIDMÜLLER B2CF 3.50/12/180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560-25/50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,8 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 x 20 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 W</t>
+  </si>
+  <si>
     <t xml:space="preserve">24-560 VDC</t>
   </si>
   <si>
-    <t xml:space="preserve">10kW</t>
+    <t xml:space="preserve">33 kW</t>
   </si>
   <si>
     <t xml:space="preserve">60 A</t>
@@ -527,9 +581,6 @@
     <t xml:space="preserve">900 W</t>
   </si>
   <si>
-    <t xml:space="preserve">VSTUPY/VÝSTUPY</t>
-  </si>
-  <si>
     <t xml:space="preserve">šroubovací svorky M8x12</t>
   </si>
   <si>
@@ -539,18 +590,9 @@
     <t xml:space="preserve">2 x 4pin  WEIDMÜLLER LSF</t>
   </si>
   <si>
-    <t xml:space="preserve">2 x 8pin WEIDMÜLLER B2CF 3.50/08/180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 12pin WEIDMÜLLER B2CF 3.50/12/180</t>
-  </si>
-  <si>
     <t xml:space="preserve">Filtr obsahující napájecí modul TGS-560</t>
   </si>
   <si>
-    <t xml:space="preserve">33 kW</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vstupní napětí (VAC - 50/60 Hz) </t>
   </si>
   <si>
@@ -560,9 +602,6 @@
     <t xml:space="preserve">Maximální vstupní proud (AC) </t>
   </si>
   <si>
-    <t xml:space="preserve">16 A</t>
-  </si>
-  <si>
     <t xml:space="preserve">Výstupní napětí (DC) </t>
   </si>
   <si>
@@ -659,19 +698,10 @@
     <t xml:space="preserve">400 W</t>
   </si>
   <si>
-    <t xml:space="preserve">100 W</t>
-  </si>
-  <si>
     <t xml:space="preserve">32 A</t>
   </si>
   <si>
-    <t xml:space="preserve">1 x 5pin WEIDMÜLLER BCZ 3.81/05/180F</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 W</t>
   </si>
   <si>
     <t xml:space="preserve">63 A</t>
@@ -3946,224 +3976,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="0" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>150</v>
+      <c r="B5" s="0" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="0" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+      <c r="B7" s="0" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>157</v>
+      <c r="B8" s="0" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="0" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="0" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="0" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="0" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>159</v>
+      <c r="B24" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>160</v>
+      <c r="B25" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>51</v>
+      <c r="B26" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>161</v>
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A28" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>163</v>
+      <c r="B28" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A31" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>164</v>
+      <c r="B31" s="0" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4182,224 +4204,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>155</v>
+      <c r="B4" s="0" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>150</v>
+      <c r="B5" s="0" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>156</v>
+      <c r="B6" s="0" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+      <c r="B7" s="0" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>157</v>
+      <c r="B8" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="0" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="0" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="0" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="0" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>159</v>
+      <c r="B24" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>160</v>
+      <c r="B25" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>51</v>
+      <c r="B26" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>161</v>
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A28" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>163</v>
+      <c r="B28" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A31" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>164</v>
+      <c r="B31" s="0" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4418,224 +4432,216 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="0" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>155</v>
+      <c r="B4" s="0" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>150</v>
+      <c r="B5" s="0" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>156</v>
+      <c r="B6" s="0" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>47</v>
+      <c r="B7" s="0" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>157</v>
+      <c r="B8" s="0" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="0" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="0" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="0" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="0" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="0" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="0" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="0" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>159</v>
+      <c r="B24" s="0" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>160</v>
+      <c r="B25" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>51</v>
+      <c r="B26" s="0" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>161</v>
+      <c r="A27" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A28" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>163</v>
+      <c r="B28" s="0" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A31" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>164</v>
+      <c r="B31" s="0" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -4682,7 +4688,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4690,7 +4696,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4706,7 +4712,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4722,7 +4728,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4767,7 +4773,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>1</v>
@@ -4818,7 +4824,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4826,7 +4832,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4842,7 +4848,7 @@
         <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4850,7 +4856,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4858,7 +4864,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4871,7 +4877,7 @@
         <v>121</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -4908,16 +4914,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>169</v>
@@ -4926,73 +4932,73 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5007,7 +5013,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -5015,18 +5021,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5042,12 +5048,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -5055,7 +5061,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>128</v>
@@ -5063,18 +5069,18 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -5111,16 +5117,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -5129,25 +5135,25 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -5156,25 +5162,25 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>1</v>
@@ -5183,19 +5189,19 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5210,7 +5216,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>1</v>
@@ -5218,18 +5224,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5245,12 +5251,12 @@
         <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>1</v>
@@ -5261,12 +5267,12 @@
         <v>36</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>1</v>
@@ -5274,7 +5280,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>1</v>
@@ -5282,10 +5288,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -5330,16 +5336,16 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>46</v>
@@ -5348,16 +5354,16 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>46</v>
@@ -5366,7 +5372,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>56</v>
@@ -5375,25 +5381,25 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
@@ -5402,19 +5408,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5429,7 +5435,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -5437,18 +5443,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5464,12 +5470,12 @@
         <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>1</v>
@@ -5480,47 +5486,47 @@
         <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -5557,28 +5563,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5596,19 +5602,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5623,28 +5629,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5662,16 +5668,16 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>1</v>
@@ -5679,10 +5685,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5690,15 +5696,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -5735,28 +5741,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5801,10 +5807,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -5822,10 +5828,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -5834,7 +5840,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -5843,7 +5849,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -5854,7 +5860,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5915,28 +5921,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5981,10 +5987,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -6002,10 +6008,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -6014,7 +6020,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -6026,7 +6032,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6284,107 +6290,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6392,16 +6398,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -6427,16 +6433,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -6462,16 +6468,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -6497,16 +6503,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -6532,16 +6538,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -6567,16 +6573,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -6602,16 +6608,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -6637,16 +6643,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -6698,89 +6704,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6800,7 +6806,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -6829,7 +6835,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -6858,7 +6864,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -6887,7 +6893,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -6916,7 +6922,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -6945,7 +6951,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -6984,44 +6990,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7029,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -7043,7 +7049,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="21"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="24"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="310">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -686,6 +686,9 @@
     <t xml:space="preserve">3 x 400 VAC</t>
   </si>
   <si>
+    <t xml:space="preserve">32 A</t>
+  </si>
+  <si>
     <t xml:space="preserve">560 VDC</t>
   </si>
   <si>
@@ -698,7 +701,31 @@
     <t xml:space="preserve">400 W</t>
   </si>
   <si>
-    <t xml:space="preserve">32 A</t>
+    <t xml:space="preserve">9 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doporučené jištění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jistič 32 A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC IN konektor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BVF 7.62HP/04/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 6pin WEIDMÜLLER BVF 7.62HP/06/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BCZ 3.81/04/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzdný odpor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 3pin WEIDMÜLLER BLZ 7.62HP/03/180F</t>
   </si>
   <si>
     <t xml:space="preserve">3 x 400 VAC/50Hz 63A</t>
@@ -3979,212 +4006,212 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4207,212 +4234,212 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4435,212 +4462,212 @@
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5099,7 +5126,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.22"/>
@@ -5129,7 +5156,7 @@
         <v>182</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>211</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -5138,7 +5165,7 @@
         <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5147,7 +5174,7 @@
         <v>185</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -5165,7 +5192,7 @@
         <v>189</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -5174,7 +5201,7 @@
         <v>191</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5183,7 +5210,7 @@
         <v>193</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>216</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -5198,10 +5225,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -5272,10 +5299,10 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5283,7 +5310,7 @@
         <v>206</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5291,7 +5318,15 @@
         <v>208</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>209</v>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5339,7 +5374,7 @@
         <v>180</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C3" s="3"/>
     </row>
@@ -5357,7 +5392,7 @@
         <v>183</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C5" s="3"/>
     </row>
@@ -5393,7 +5428,7 @@
         <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -5420,7 +5455,7 @@
         <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5494,7 +5529,7 @@
         <v>205</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5515,7 +5550,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>209</v>
@@ -5523,10 +5558,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -5563,28 +5598,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5602,19 +5637,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -5629,28 +5664,28 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C12" s="3"/>
     </row>
@@ -5668,10 +5703,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C15" s="3"/>
     </row>
@@ -5685,10 +5720,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5696,15 +5731,15 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -5741,28 +5776,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5807,10 +5842,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -5828,10 +5863,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -5849,7 +5884,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>37</v>
@@ -5860,7 +5895,7 @@
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5921,28 +5956,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3"/>
     </row>
@@ -5987,10 +6022,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -6008,10 +6043,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C13" s="3"/>
     </row>
@@ -6032,7 +6067,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6290,107 +6325,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6398,16 +6433,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>2.05</v>
@@ -6433,16 +6468,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>2.05</v>
@@ -6468,16 +6503,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>2.05</v>
@@ -6503,16 +6538,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>2.05</v>
@@ -6538,16 +6573,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>2.05</v>
@@ -6573,16 +6608,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>2.05</v>
@@ -6608,16 +6643,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1.25</v>
@@ -6643,16 +6678,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1.25</v>
@@ -6704,89 +6739,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6806,7 +6841,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>300</v>
@@ -6835,7 +6870,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>300</v>
@@ -6864,7 +6899,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>300</v>
@@ -6893,7 +6928,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>300</v>
@@ -6922,7 +6957,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>300</v>
@@ -6951,7 +6986,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="G9" s="1" t="n">
         <v>300</v>
@@ -6990,44 +7025,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7035,7 +7070,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>11</v>
@@ -7049,7 +7084,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>11</v>

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -713,10 +713,10 @@
     <t xml:space="preserve">AC IN konektor</t>
   </si>
   <si>
-    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BVF 7.62HP/04/180F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 x 6pin WEIDMÜLLER BVF 7.62HP/06/180F</t>
+    <t xml:space="preserve">1 x 4pin WEIDMÜLLER BVZ 7.62HP/04/180F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 6pin WEIDMÜLLER BVZ 7.62HP/06/180F</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 4pin WEIDMÜLLER BCZ 3.81/04/180F</t>

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="21"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="37"/>
   </bookViews>
   <sheets>
     <sheet name="TGZ-D-48-13_26" sheetId="1" state="visible" r:id="rId3"/>
@@ -45,13 +45,14 @@
     <sheet name="TGS-560-25_50" sheetId="35" state="visible" r:id="rId37"/>
     <sheet name="TGS-560-50_100" sheetId="36" state="visible" r:id="rId38"/>
     <sheet name="TGMmini" sheetId="37" state="visible" r:id="rId39"/>
-    <sheet name="TGMcontroller" sheetId="38" state="visible" r:id="rId40"/>
-    <sheet name="TGZpMotion" sheetId="39" state="visible" r:id="rId41"/>
-    <sheet name="X8_commonHW_DI_tab" sheetId="40" state="visible" r:id="rId42"/>
-    <sheet name="X8_commonHW_DI_RI_tab" sheetId="41" state="visible" r:id="rId43"/>
-    <sheet name="X8_commonHW_DO_tab" sheetId="42" state="visible" r:id="rId44"/>
-    <sheet name="X8_commonHW_AI_tab" sheetId="43" state="visible" r:id="rId45"/>
-    <sheet name="TGmonitor7" sheetId="44" state="visible" r:id="rId46"/>
+    <sheet name="TGZ-D-48-50_100-UNIR-RI" sheetId="38" state="visible" r:id="rId40"/>
+    <sheet name="TGMcontroller" sheetId="39" state="visible" r:id="rId41"/>
+    <sheet name="TGZpMotion" sheetId="40" state="visible" r:id="rId42"/>
+    <sheet name="X8_commonHW_DI_tab" sheetId="41" state="visible" r:id="rId43"/>
+    <sheet name="X8_commonHW_DI_RI_tab" sheetId="42" state="visible" r:id="rId44"/>
+    <sheet name="X8_commonHW_DO_tab" sheetId="43" state="visible" r:id="rId45"/>
+    <sheet name="X8_commonHW_AI_tab" sheetId="44" state="visible" r:id="rId46"/>
+    <sheet name="TGmonitor7" sheetId="45" state="visible" r:id="rId47"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="339">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -225,6 +226,9 @@
   </si>
   <si>
     <t xml:space="preserve">1 x 3pin WAGO push-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x 5pin WEIDMÜLLER  BCZ 3.81/05/180F</t>
   </si>
   <si>
     <t xml:space="preserve">1 x 4pin WAGO push-in</t>
@@ -1237,37 +1241,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1583,7 +1587,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1615,7 +1619,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1623,7 +1627,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1639,7 +1643,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1655,12 +1659,12 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -1668,23 +1672,23 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -1692,18 +1696,18 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1724,7 +1728,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
@@ -1740,18 +1744,18 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1767,23 +1771,23 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1802,7 +1806,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="39.93"/>
@@ -1822,7 +1826,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1846,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1854,7 +1858,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1862,7 +1866,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1878,7 +1882,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1894,7 +1898,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1902,7 +1906,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1910,12 +1914,12 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -1923,23 +1927,23 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
@@ -1947,98 +1951,106 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1</v>
+      <c r="B31" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2089,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2101,7 +2113,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,7 +2121,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,7 +2129,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2181,7 +2193,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2202,10 +2214,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2221,7 +2233,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2241,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2237,15 +2249,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2253,7 +2265,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2261,15 +2273,15 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2320,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2332,7 +2344,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2340,7 +2352,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2348,7 +2360,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2412,7 +2424,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2433,10 +2445,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2452,7 +2464,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2460,7 +2472,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2468,15 +2480,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2484,7 +2496,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2492,23 +2504,23 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2547,7 +2559,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2571,7 +2583,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2579,7 +2591,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2587,7 +2599,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,7 +2663,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2672,10 +2684,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2691,7 +2703,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2699,7 +2711,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2707,15 +2719,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2723,7 +2735,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2731,23 +2743,23 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -2786,7 +2798,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2810,7 +2822,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,7 +2830,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2826,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2911,7 +2923,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
@@ -2930,7 +2942,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2938,7 +2950,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2946,15 +2958,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,10 +2987,10 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3017,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3041,7 +3053,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3049,7 +3061,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3057,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3121,7 +3133,7 @@
         <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3142,10 +3154,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3161,7 +3173,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3169,7 +3181,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,15 +3189,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3193,7 +3205,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,23 +3213,23 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3256,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3264,7 +3276,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3272,7 +3284,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3280,7 +3292,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3296,7 +3308,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3381,7 +3393,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
@@ -3400,7 +3412,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3408,7 +3420,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3416,7 +3428,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3424,7 +3436,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3432,21 +3444,21 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3485,7 +3497,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3493,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3501,7 +3513,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3509,7 +3521,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3525,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3619,7 +3631,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
@@ -3641,7 +3653,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3649,7 +3661,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3657,7 +3669,7 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3665,7 +3677,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3673,7 +3685,7 @@
         <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3681,16 +3693,16 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6729,7 +6741,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6737,7 +6749,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6745,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6753,7 +6765,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6769,7 +6781,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,7 +6797,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6801,7 +6813,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6809,7 +6821,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6817,12 +6829,12 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -6830,23 +6842,23 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
@@ -6854,18 +6866,18 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6886,10 +6898,10 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6905,7 +6917,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6913,7 +6925,7 @@
         <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6921,21 +6933,21 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -7134,7 +7146,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7142,15 +7154,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7205,7 +7217,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7213,7 +7225,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7221,7 +7233,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7229,7 +7241,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7245,7 +7257,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7261,7 +7273,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7277,12 +7289,12 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -7290,23 +7302,23 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -7314,18 +7326,18 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7346,10 +7358,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7365,7 +7377,7 @@
         <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7373,7 +7385,7 @@
         <v>38</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7381,21 +7393,21 @@
         <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -7434,7 +7446,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7442,7 +7454,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7450,7 +7462,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7458,7 +7470,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7466,7 +7478,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7474,15 +7486,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7498,7 +7510,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7517,7 +7529,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7525,7 +7537,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7533,12 +7545,12 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -7546,23 +7558,23 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -7570,18 +7582,18 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7602,10 +7614,10 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7621,7 +7633,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7629,7 +7641,7 @@
         <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7637,21 +7649,21 @@
         <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -7670,7 +7682,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.55"/>
@@ -7690,7 +7702,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7698,7 +7710,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7706,7 +7718,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7714,7 +7726,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7722,7 +7734,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7730,15 +7742,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7754,7 +7766,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7773,7 +7785,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7781,7 +7793,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7789,12 +7801,12 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -7802,23 +7814,23 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1</v>
@@ -7826,63 +7838,63 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>140</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>141</v>
@@ -7890,24 +7902,32 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="2"/>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>148</v>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -7946,7 +7966,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7954,7 +7974,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7962,7 +7982,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7970,7 +7990,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7978,7 +7998,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7986,15 +8006,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8010,7 +8030,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8029,12 +8049,12 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -8042,23 +8062,23 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>1</v>
@@ -8066,18 +8086,18 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8098,10 +8118,10 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8117,7 +8137,7 @@
         <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8125,7 +8145,7 @@
         <v>38</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8133,21 +8153,21 @@
         <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -8194,7 +8214,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8202,7 +8222,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8210,7 +8230,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8218,7 +8238,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8226,7 +8246,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,7 +8358,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8346,7 +8366,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8354,7 +8374,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8362,7 +8382,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8370,7 +8390,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8417,7 +8437,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8425,7 +8445,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8433,7 +8453,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8441,7 +8461,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8561,7 +8581,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8569,7 +8589,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8577,7 +8597,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8585,7 +8605,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8593,7 +8613,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8632,7 +8652,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8640,7 +8660,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8648,7 +8668,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8656,7 +8676,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8664,7 +8684,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8672,15 +8692,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8777,7 +8797,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>34</v>
@@ -8800,7 +8820,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8808,7 +8828,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8816,7 +8836,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8824,7 +8844,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8832,7 +8852,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8841,16 +8861,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -8889,7 +8909,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8897,7 +8917,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8905,7 +8925,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8913,7 +8933,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8934,10 +8954,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9034,7 +9054,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>34</v>
@@ -9057,7 +9077,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9065,7 +9085,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9073,7 +9093,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9081,7 +9101,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9089,7 +9109,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9098,16 +9118,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -9146,7 +9166,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9154,7 +9174,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9162,7 +9182,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9170,7 +9190,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9178,7 +9198,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9186,15 +9206,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9291,7 +9311,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>34</v>
@@ -9314,7 +9334,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9322,7 +9342,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9330,7 +9350,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9338,7 +9358,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9346,7 +9366,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9355,16 +9375,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -9403,7 +9423,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9411,7 +9431,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9419,7 +9439,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9427,7 +9447,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9435,7 +9455,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9443,15 +9463,15 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9548,7 +9568,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>34</v>
@@ -9571,7 +9591,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9579,7 +9599,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9587,7 +9607,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9595,7 +9615,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9603,7 +9623,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9612,16 +9632,16 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -9676,7 +9696,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9684,7 +9704,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9692,7 +9712,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9700,7 +9720,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9785,7 +9805,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
@@ -9804,7 +9824,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9812,7 +9832,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9820,15 +9840,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9883,7 +9903,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9891,7 +9911,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9899,7 +9919,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9907,7 +9927,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9915,7 +9935,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9923,7 +9943,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9931,7 +9951,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9984,7 +10004,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -10035,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10043,7 +10063,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10051,7 +10071,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10059,7 +10079,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10067,20 +10087,20 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -10119,7 +10139,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10127,7 +10147,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10135,7 +10155,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10143,7 +10163,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10151,7 +10171,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10167,7 +10187,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10220,7 +10240,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -10271,7 +10291,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10279,7 +10299,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10287,7 +10307,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10295,7 +10315,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10303,20 +10323,20 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -10355,7 +10375,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10363,7 +10383,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10371,7 +10391,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10379,7 +10399,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10387,7 +10407,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10395,7 +10415,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10403,7 +10423,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10456,7 +10476,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -10507,7 +10527,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10515,7 +10535,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10523,7 +10543,7 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10531,7 +10551,7 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10539,20 +10559,20 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -10591,7 +10611,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10599,7 +10619,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10607,7 +10627,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10615,7 +10635,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10623,7 +10643,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10639,7 +10659,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10692,7 +10712,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1</v>
@@ -10743,7 +10763,7 @@
         <v>36</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10751,7 +10771,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10759,15 +10779,15 @@
         <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10775,7 +10795,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10783,20 +10803,20 @@
         <v>44</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -10833,46 +10853,46 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -10881,43 +10901,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -10941,7 +10961,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -10949,18 +10969,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10973,15 +10993,15 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>1</v>
@@ -10989,26 +11009,26 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -11045,43 +11065,43 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>49</v>
@@ -11093,43 +11113,43 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -11153,7 +11173,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1</v>
@@ -11161,18 +11181,18 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11185,15 +11205,15 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>1</v>
@@ -11204,39 +11224,39 @@
         <v>38</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -11276,21 +11296,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>49</v>
@@ -11299,16 +11319,16 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>49</v>
@@ -11317,10 +11337,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -11329,22 +11349,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -11353,19 +11373,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -11389,7 +11409,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -11397,18 +11417,18 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11421,15 +11441,15 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>1</v>
@@ -11440,47 +11460,47 @@
         <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -11517,28 +11537,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -11565,19 +11585,19 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C9" s="2"/>
     </row>
@@ -11592,28 +11612,28 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -11631,16 +11651,16 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -11648,10 +11668,10 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11659,15 +11679,15 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -11686,12 +11706,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11704,165 +11723,252 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>242</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>244</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="2"/>
+        <v>52</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>257</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>259</v>
+        <v>72</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>103</v>
+        <v>74</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
@@ -11875,7 +11981,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.22"/>
@@ -11893,28 +11999,28 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -11968,10 +12074,10 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C11" s="2"/>
     </row>
@@ -11989,10 +12095,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -12001,7 +12107,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -12010,18 +12116,42 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>259</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>103</v>
+      <c r="B19" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -12076,7 +12206,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12084,7 +12214,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12092,7 +12222,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12100,7 +12230,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12116,7 +12246,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12132,7 +12262,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12140,7 +12270,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12148,12 +12278,12 @@
         <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -12161,18 +12291,18 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12180,7 +12310,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
@@ -12188,18 +12318,18 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12220,7 +12350,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>34</v>
@@ -12236,18 +12366,18 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12263,15 +12393,15 @@
         <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -12286,6 +12416,171 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="42.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="45.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12306,107 +12601,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12414,16 +12709,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2.05</v>
@@ -12449,16 +12744,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2.05</v>
@@ -12484,16 +12779,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2.05</v>
@@ -12519,16 +12814,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2.05</v>
@@ -12554,16 +12849,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2.05</v>
@@ -12589,16 +12884,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2.05</v>
@@ -12624,16 +12919,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1.25</v>
@@ -12659,16 +12954,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1.25</v>
@@ -12700,7 +12995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12720,98 +13015,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12819,10 +13114,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>24</v>
@@ -12851,10 +13146,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>24</v>
@@ -12883,10 +13178,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>24</v>
@@ -12915,10 +13210,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>24</v>
@@ -12947,10 +13242,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>24</v>
@@ -12979,10 +13274,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>24</v>
@@ -13011,10 +13306,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>24</v>
@@ -13043,10 +13338,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>24</v>
@@ -13081,7 +13376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -13101,89 +13396,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13203,7 +13498,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>300</v>
@@ -13232,7 +13527,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>300</v>
@@ -13261,7 +13556,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>300</v>
@@ -13290,7 +13585,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>300</v>
@@ -13319,7 +13614,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>300</v>
@@ -13348,7 +13643,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>300</v>
@@ -13358,101 +13653,6 @@
       </c>
       <c r="I9" s="2" t="n">
         <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -13471,6 +13671,101 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -13489,24 +13784,24 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
@@ -13514,32 +13809,32 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -13547,66 +13842,66 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13681,7 +13976,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13689,7 +13984,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13697,7 +13992,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13705,7 +14000,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13721,7 +14016,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13737,12 +14032,12 @@
         <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -13750,18 +14045,18 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13769,7 +14064,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -13777,18 +14072,18 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13809,7 +14104,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
@@ -13825,18 +14120,18 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13852,15 +14147,15 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -13899,7 +14194,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13923,7 +14218,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13931,7 +14226,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13939,7 +14234,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13955,7 +14250,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13971,12 +14266,12 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1</v>
@@ -13984,23 +14279,23 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1</v>
@@ -14008,18 +14303,18 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14040,7 +14335,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
@@ -14056,18 +14351,18 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14083,23 +14378,23 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -14138,7 +14433,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14162,7 +14457,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14170,7 +14465,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14178,7 +14473,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14194,7 +14489,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14210,7 +14505,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14218,7 +14513,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14226,12 +14521,12 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -14239,23 +14534,23 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
@@ -14263,18 +14558,18 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14295,7 +14590,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>34</v>
@@ -14311,18 +14606,18 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14338,23 +14633,23 @@
         <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -14393,7 +14688,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14417,7 +14712,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14425,7 +14720,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14433,7 +14728,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14449,7 +14744,7 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14465,7 +14760,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14473,7 +14768,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14481,12 +14776,12 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>1</v>
@@ -14494,23 +14789,23 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1</v>
@@ -14518,26 +14813,26 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14558,7 +14853,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>34</v>
@@ -14574,18 +14869,18 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14601,23 +14896,23 @@
         <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -14656,7 +14951,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14680,7 +14975,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14688,7 +14983,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14696,7 +14991,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14781,7 +15076,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
@@ -14800,7 +15095,7 @@
         <v>36</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14808,7 +15103,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14816,15 +15111,15 @@
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14845,10 +15140,10 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/tab/parameters.xlsx
+++ b/Manual/source/tab/parameters.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="340">
   <si>
     <t xml:space="preserve">NAPÁJENÍ</t>
   </si>
@@ -853,6 +853,9 @@
   </si>
   <si>
     <t xml:space="preserve">2 x 10pin WEIDMÜLLER B2CF 3.50/10/180 SN OR BX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–48 VDC (jištění 100 A)</t>
   </si>
   <si>
     <t xml:space="preserve">Červená/zelená dioda</t>
@@ -11734,7 +11737,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12098,7 +12101,7 @@
         <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -12537,7 +12540,7 @@
         <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -12601,107 +12604,107 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12709,16 +12712,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>2.05</v>
@@ -12744,16 +12747,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>2.05</v>
@@ -12779,16 +12782,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>2.05</v>
@@ -12814,16 +12817,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2.05</v>
@@ -12849,16 +12852,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2.05</v>
@@ -12884,16 +12887,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2.05</v>
@@ -12919,16 +12922,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1.25</v>
@@ -12954,16 +12957,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1.25</v>
@@ -13015,98 +13018,98 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13114,10 +13117,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>24</v>
@@ -13146,10 +13149,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>24</v>
@@ -13178,10 +13181,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>24</v>
@@ -13210,10 +13213,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>24</v>
@@ -13242,10 +13245,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>24</v>
@@ -13274,10 +13277,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>24</v>
@@ -13306,10 +13309,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>24</v>
@@ -13338,10 +13341,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>24</v>
@@ -13396,89 +13399,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13498,7 +13501,7 @@
         <v>0.5</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>300</v>
@@ -13527,7 +13530,7 @@
         <v>0.5</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>300</v>
@@ -13556,7 +13559,7 @@
         <v>0.5</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>300</v>
@@ -13585,7 +13588,7 @@
         <v>0.5</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>300</v>
@@ -13614,7 +13617,7 @@
         <v>0.5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>300</v>
@@ -13643,7 +13646,7 @@
         <v>0.5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>300</v>
@@ -13682,44 +13685,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13727,7 +13730,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>11</v>
@@ -13741,7 +13744,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>11</v>
@@ -13792,10 +13795,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -13834,7 +13837,7 @@
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1</v>
@@ -13842,66 +13845,66 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
